--- a/策划/excel/1_Role.xlsx
+++ b/策划/excel/1_Role.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="30435" windowHeight="15735"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="1_Role" state="visible" r:id="rId4"/>
   </sheets>
@@ -11,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -85,16 +88,13 @@
     <t>client</t>
   </si>
   <si>
-    <t>猫骑士</t>
-  </si>
-  <si>
-    <t>执巨剑与猫纹盾的铁盔近卫</t>
-  </si>
-  <si>
-    <t>稳定的攻防角色，善于把冠面转化为护甲与追加伤害，适合第一局体验。</t>
-  </si>
-  <si>
-    <t>[20001,20001,20001,20003,20003,20002,20002,20002,20002,20004]</t>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>无畏的战士</t>
+  </si>
+  <si>
+    <t>[20032,20032,20032,20042,20042,20033,20033,20033,20033,20031]</t>
   </si>
   <si>
     <t>[[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6]]</t>
@@ -443,19 +443,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="28.75" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="7" max="7" width="36.733333587646484" customWidth="1"/>
-    <col min="8" max="8" width="53.69166564941406" customWidth="1"/>
+    <col min="7" max="7" width="36.7333333333333" customWidth="1"/>
+    <col min="8" max="8" width="53.6916666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -614,7 +615,7 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -623,10 +624,10 @@
         <v>100</v>
       </c>
       <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
         <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -637,13 +638,13 @@
         <v>10002</v>
       </c>
       <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -652,10 +653,10 @@
         <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7">
         <v>6</v>
@@ -666,13 +667,13 @@
         <v>10003</v>
       </c>
       <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
         <v>33</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
       </c>
       <c r="E8">
         <v>90</v>
@@ -681,10 +682,10 @@
         <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>6</v>
